--- a/tracking_forms/033_travel_log_form_template--tracking_forms.xlsx
+++ b/tracking_forms/033_travel_log_form_template--tracking_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -895,8 +895,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="27" customWidth="1" min="1" max="1"/>
-    <col width="50" customWidth="1" min="2" max="2"/>
-    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="10" customWidth="1" min="2" max="2"/>
+    <col width="10" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -924,12 +924,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'id':_81,_'name':_'car',_'value':_'car'}</t>
+          <t>car</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'id': 81, 'name': 'car', 'value': 'car'}</t>
+          <t>car</t>
         </is>
       </c>
     </row>
@@ -941,12 +941,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'id':_82,_'name':_'bus',_'value':_'bus'}</t>
+          <t>bus</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'id': 82, 'name': 'bus', 'value': 'bus'}</t>
+          <t>bus</t>
         </is>
       </c>
     </row>
@@ -958,12 +958,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'id':_82,_'name':_'plane',_'value':_'plane'}</t>
+          <t>plane</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'id': 82, 'name': 'plane', 'value': 'plane'}</t>
+          <t>plane</t>
         </is>
       </c>
     </row>
@@ -975,12 +975,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'id':_83,_'name':_'train',_'value':_'train'}</t>
+          <t>train</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'id': 83, 'name': 'train', 'value': 'train'}</t>
+          <t>train</t>
         </is>
       </c>
     </row>
@@ -992,12 +992,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'id':_84,_'name':_'bike',_'value':_'bike'}</t>
+          <t>bike</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'id': 84, 'name': 'bike', 'value': 'bike'}</t>
+          <t>bike</t>
         </is>
       </c>
     </row>
@@ -1009,12 +1009,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'id':_85,_'name':_'other',_'value':_'other'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'id': 85, 'name': 'other', 'value': 'other'}</t>
+          <t>other</t>
         </is>
       </c>
     </row>
@@ -1026,12 +1026,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'id':_131,_'name':_'jim',_'value':_'jimmmy'}</t>
+          <t>jimmmy</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'id': 131, 'name': 'Jim', 'value': 'jimmmy'}</t>
+          <t>jimmmy</t>
         </is>
       </c>
     </row>
@@ -1043,12 +1043,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'id':_132,_'name':_'jane',_'value':_'jane'}</t>
+          <t>jane</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'id': 132, 'name': 'Jane', 'value': 'jane'}</t>
+          <t>jane</t>
         </is>
       </c>
     </row>
@@ -1060,12 +1060,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'id':_132,_'name':_'john',_'value':_'john'}</t>
+          <t>john</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'id': 132, 'name': 'John', 'value': 'john'}</t>
+          <t>john</t>
         </is>
       </c>
     </row>
@@ -1077,12 +1077,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'id':_141,_'name':_'approved',_'value':_'approved'}</t>
+          <t>approved</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'id': 141, 'name': 'approved', 'value': 'approved'}</t>
+          <t>approved</t>
         </is>
       </c>
     </row>
@@ -1094,12 +1094,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'id':_142,_'name':_'pending',_'value':_'pending'}</t>
+          <t>pending</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'id': 142, 'name': 'pending', 'value': 'pending'}</t>
+          <t>pending</t>
         </is>
       </c>
     </row>
